--- a/web/public/forms/doseo-pyoji.xlsx
+++ b/web/public/forms/doseo-pyoji.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="도서 표지 모음" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'도서 표지 모음'!$A$1:$X$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0;;&quot;&quot;"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,32 +37,53 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000F203F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="006B7280"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="00111827"/>
       <sz val="19"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,12 +92,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F8FC"/>
+        <fgColor rgb="00F3F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3FB"/>
+        <fgColor rgb="00E8EEF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF4FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,23 +116,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,32 +141,53 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -530,15 +583,15 @@
     <col width="3.6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵   |   k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다   </t>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
         </is>
       </c>
     </row>
@@ -596,7 +649,7 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
@@ -626,7 +679,7 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
@@ -656,7 +709,7 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
@@ -686,7 +739,7 @@
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="G9" s="7" t="n"/>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
@@ -716,7 +769,7 @@
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="n"/>
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
@@ -746,7 +799,7 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="n"/>
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
@@ -767,7 +820,7 @@
     </row>
     <row r="12" ht="6" customHeight="1"/>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>※ 아래는 목차입니다.</t>
         </is>
@@ -775,13 +828,13 @@
     </row>
     <row r="14" ht="6" customHeight="1"/>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
       <c r="B15" s="5" t="n"/>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>제        목</t>
         </is>
@@ -804,7 +857,7 @@
       <c r="S15" s="5" t="n"/>
       <c r="T15" s="5" t="n"/>
       <c r="U15" s="5" t="n"/>
-      <c r="V15" s="8" t="inlineStr">
+      <c r="V15" s="9" t="inlineStr">
         <is>
           <t>면</t>
         </is>
@@ -813,9 +866,12 @@
       <c r="X15" s="5" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="9" t="inlineStr"/>
+      <c r="A16" s="10">
+        <f>IF(C16="","",COUNTA(C16:C16))</f>
+        <v/>
+      </c>
       <c r="B16" s="5" t="n"/>
-      <c r="C16" s="9" t="inlineStr"/>
+      <c r="C16" s="11" t="n"/>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
@@ -834,14 +890,17 @@
       <c r="S16" s="5" t="n"/>
       <c r="T16" s="5" t="n"/>
       <c r="U16" s="5" t="n"/>
-      <c r="V16" s="9" t="inlineStr"/>
+      <c r="V16" s="12" t="n"/>
       <c r="W16" s="5" t="n"/>
       <c r="X16" s="5" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="9" t="inlineStr"/>
+      <c r="A17" s="10">
+        <f>IF(C17="","",COUNTA(C16:C17))</f>
+        <v/>
+      </c>
       <c r="B17" s="5" t="n"/>
-      <c r="C17" s="9" t="inlineStr"/>
+      <c r="C17" s="11" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
@@ -860,14 +919,17 @@
       <c r="S17" s="5" t="n"/>
       <c r="T17" s="5" t="n"/>
       <c r="U17" s="5" t="n"/>
-      <c r="V17" s="9" t="inlineStr"/>
+      <c r="V17" s="12" t="n"/>
       <c r="W17" s="5" t="n"/>
       <c r="X17" s="5" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="9" t="inlineStr"/>
+      <c r="A18" s="10">
+        <f>IF(C18="","",COUNTA(C16:C18))</f>
+        <v/>
+      </c>
       <c r="B18" s="5" t="n"/>
-      <c r="C18" s="9" t="inlineStr"/>
+      <c r="C18" s="11" t="n"/>
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
@@ -886,14 +948,17 @@
       <c r="S18" s="5" t="n"/>
       <c r="T18" s="5" t="n"/>
       <c r="U18" s="5" t="n"/>
-      <c r="V18" s="9" t="inlineStr"/>
+      <c r="V18" s="12" t="n"/>
       <c r="W18" s="5" t="n"/>
       <c r="X18" s="5" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="9" t="inlineStr"/>
+      <c r="A19" s="10">
+        <f>IF(C19="","",COUNTA(C16:C19))</f>
+        <v/>
+      </c>
       <c r="B19" s="5" t="n"/>
-      <c r="C19" s="9" t="inlineStr"/>
+      <c r="C19" s="11" t="n"/>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
@@ -912,14 +977,17 @@
       <c r="S19" s="5" t="n"/>
       <c r="T19" s="5" t="n"/>
       <c r="U19" s="5" t="n"/>
-      <c r="V19" s="9" t="inlineStr"/>
+      <c r="V19" s="12" t="n"/>
       <c r="W19" s="5" t="n"/>
       <c r="X19" s="5" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="9" t="inlineStr"/>
+      <c r="A20" s="10">
+        <f>IF(C20="","",COUNTA(C16:C20))</f>
+        <v/>
+      </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="9" t="inlineStr"/>
+      <c r="C20" s="11" t="n"/>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
@@ -938,14 +1006,17 @@
       <c r="S20" s="5" t="n"/>
       <c r="T20" s="5" t="n"/>
       <c r="U20" s="5" t="n"/>
-      <c r="V20" s="9" t="inlineStr"/>
+      <c r="V20" s="12" t="n"/>
       <c r="W20" s="5" t="n"/>
       <c r="X20" s="5" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="9" t="inlineStr"/>
+      <c r="A21" s="10">
+        <f>IF(C21="","",COUNTA(C16:C21))</f>
+        <v/>
+      </c>
       <c r="B21" s="5" t="n"/>
-      <c r="C21" s="9" t="inlineStr"/>
+      <c r="C21" s="11" t="n"/>
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
@@ -964,14 +1035,17 @@
       <c r="S21" s="5" t="n"/>
       <c r="T21" s="5" t="n"/>
       <c r="U21" s="5" t="n"/>
-      <c r="V21" s="9" t="inlineStr"/>
+      <c r="V21" s="12" t="n"/>
       <c r="W21" s="5" t="n"/>
       <c r="X21" s="5" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="9" t="inlineStr"/>
+      <c r="A22" s="10">
+        <f>IF(C22="","",COUNTA(C16:C22))</f>
+        <v/>
+      </c>
       <c r="B22" s="5" t="n"/>
-      <c r="C22" s="9" t="inlineStr"/>
+      <c r="C22" s="11" t="n"/>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
@@ -990,14 +1064,17 @@
       <c r="S22" s="5" t="n"/>
       <c r="T22" s="5" t="n"/>
       <c r="U22" s="5" t="n"/>
-      <c r="V22" s="9" t="inlineStr"/>
+      <c r="V22" s="12" t="n"/>
       <c r="W22" s="5" t="n"/>
       <c r="X22" s="5" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="9" t="inlineStr"/>
+      <c r="A23" s="10">
+        <f>IF(C23="","",COUNTA(C16:C23))</f>
+        <v/>
+      </c>
       <c r="B23" s="5" t="n"/>
-      <c r="C23" s="9" t="inlineStr"/>
+      <c r="C23" s="11" t="n"/>
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
@@ -1016,14 +1093,17 @@
       <c r="S23" s="5" t="n"/>
       <c r="T23" s="5" t="n"/>
       <c r="U23" s="5" t="n"/>
-      <c r="V23" s="9" t="inlineStr"/>
+      <c r="V23" s="12" t="n"/>
       <c r="W23" s="5" t="n"/>
       <c r="X23" s="5" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="9" t="inlineStr"/>
+      <c r="A24" s="10">
+        <f>IF(C24="","",COUNTA(C16:C24))</f>
+        <v/>
+      </c>
       <c r="B24" s="5" t="n"/>
-      <c r="C24" s="9" t="inlineStr"/>
+      <c r="C24" s="11" t="n"/>
       <c r="D24" s="5" t="n"/>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
@@ -1042,14 +1122,17 @@
       <c r="S24" s="5" t="n"/>
       <c r="T24" s="5" t="n"/>
       <c r="U24" s="5" t="n"/>
-      <c r="V24" s="9" t="inlineStr"/>
+      <c r="V24" s="12" t="n"/>
       <c r="W24" s="5" t="n"/>
       <c r="X24" s="5" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="9" t="inlineStr"/>
+      <c r="A25" s="10">
+        <f>IF(C25="","",COUNTA(C16:C25))</f>
+        <v/>
+      </c>
       <c r="B25" s="5" t="n"/>
-      <c r="C25" s="9" t="inlineStr"/>
+      <c r="C25" s="11" t="n"/>
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
@@ -1068,14 +1151,17 @@
       <c r="S25" s="5" t="n"/>
       <c r="T25" s="5" t="n"/>
       <c r="U25" s="5" t="n"/>
-      <c r="V25" s="9" t="inlineStr"/>
+      <c r="V25" s="12" t="n"/>
       <c r="W25" s="5" t="n"/>
       <c r="X25" s="5" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="9" t="inlineStr"/>
+      <c r="A26" s="10">
+        <f>IF(C26="","",COUNTA(C16:C26))</f>
+        <v/>
+      </c>
       <c r="B26" s="5" t="n"/>
-      <c r="C26" s="9" t="inlineStr"/>
+      <c r="C26" s="11" t="n"/>
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
@@ -1094,14 +1180,17 @@
       <c r="S26" s="5" t="n"/>
       <c r="T26" s="5" t="n"/>
       <c r="U26" s="5" t="n"/>
-      <c r="V26" s="9" t="inlineStr"/>
+      <c r="V26" s="12" t="n"/>
       <c r="W26" s="5" t="n"/>
       <c r="X26" s="5" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="9" t="inlineStr"/>
+      <c r="A27" s="10">
+        <f>IF(C27="","",COUNTA(C16:C27))</f>
+        <v/>
+      </c>
       <c r="B27" s="5" t="n"/>
-      <c r="C27" s="9" t="inlineStr"/>
+      <c r="C27" s="11" t="n"/>
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="n"/>
@@ -1120,14 +1209,17 @@
       <c r="S27" s="5" t="n"/>
       <c r="T27" s="5" t="n"/>
       <c r="U27" s="5" t="n"/>
-      <c r="V27" s="9" t="inlineStr"/>
+      <c r="V27" s="12" t="n"/>
       <c r="W27" s="5" t="n"/>
       <c r="X27" s="5" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="9" t="inlineStr"/>
+      <c r="A28" s="10">
+        <f>IF(C28="","",COUNTA(C16:C28))</f>
+        <v/>
+      </c>
       <c r="B28" s="5" t="n"/>
-      <c r="C28" s="9" t="inlineStr"/>
+      <c r="C28" s="11" t="n"/>
       <c r="D28" s="5" t="n"/>
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
@@ -1146,14 +1238,17 @@
       <c r="S28" s="5" t="n"/>
       <c r="T28" s="5" t="n"/>
       <c r="U28" s="5" t="n"/>
-      <c r="V28" s="9" t="inlineStr"/>
+      <c r="V28" s="12" t="n"/>
       <c r="W28" s="5" t="n"/>
       <c r="X28" s="5" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="9" t="inlineStr"/>
+      <c r="A29" s="10">
+        <f>IF(C29="","",COUNTA(C16:C29))</f>
+        <v/>
+      </c>
       <c r="B29" s="5" t="n"/>
-      <c r="C29" s="9" t="inlineStr"/>
+      <c r="C29" s="11" t="n"/>
       <c r="D29" s="5" t="n"/>
       <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="n"/>
@@ -1172,51 +1267,61 @@
       <c r="S29" s="5" t="n"/>
       <c r="T29" s="5" t="n"/>
       <c r="U29" s="5" t="n"/>
-      <c r="V29" s="9" t="inlineStr"/>
+      <c r="V29" s="12" t="n"/>
       <c r="W29" s="5" t="n"/>
       <c r="X29" s="5" t="n"/>
     </row>
     <row r="30" ht="6" customHeight="1"/>
     <row r="31" ht="10" customHeight="1"/>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>년        월        일</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="K33" s="11" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="14" t="inlineStr"/>
+      <c r="K33" s="15" t="inlineStr">
         <is>
           <t>현장대리인</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="Q33" s="16" t="n"/>
+      <c r="U33" s="17" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>발주기관이 정한 서식이 있으면 그 서식을 사용하세요. 이 줄과 1행은 인쇄 전에 지우셔도 됩니다.</t>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19.5" customHeight="1">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="70">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="V28:X28"/>
     <mergeCell ref="V24:X24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="G7:X7"/>
     <mergeCell ref="C27:U27"/>
+    <mergeCell ref="U33:X33"/>
     <mergeCell ref="C23:U23"/>
-    <mergeCell ref="K33:R33"/>
     <mergeCell ref="G10:X10"/>
     <mergeCell ref="C17:U17"/>
+    <mergeCell ref="A33:J33"/>
     <mergeCell ref="G6:X6"/>
     <mergeCell ref="A37:X37"/>
     <mergeCell ref="V15:X15"/>
@@ -1226,7 +1331,6 @@
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="V27:X27"/>
     <mergeCell ref="C28:U28"/>
-    <mergeCell ref="S33:X33"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:X5"/>
     <mergeCell ref="A8:F8"/>
@@ -1243,6 +1347,7 @@
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="Q33:T33"/>
     <mergeCell ref="V22:X22"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="C26:U26"/>
@@ -1260,6 +1365,7 @@
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C25:U25"/>
+    <mergeCell ref="K33:P33"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="G11:X11"/>
@@ -1270,12 +1376,907 @@
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="M1:X1"/>
     <mergeCell ref="V20:X20"/>
+    <mergeCell ref="A36:X36"/>
     <mergeCell ref="V29:X29"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="G8:X8"/>
     <mergeCell ref="V19:X19"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:X36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.6" customWidth="1" min="1" max="1"/>
+    <col width="3.6" customWidth="1" min="2" max="2"/>
+    <col width="3.6" customWidth="1" min="3" max="3"/>
+    <col width="3.6" customWidth="1" min="4" max="4"/>
+    <col width="3.6" customWidth="1" min="5" max="5"/>
+    <col width="3.6" customWidth="1" min="6" max="6"/>
+    <col width="3.6" customWidth="1" min="7" max="7"/>
+    <col width="3.6" customWidth="1" min="8" max="8"/>
+    <col width="3.6" customWidth="1" min="9" max="9"/>
+    <col width="3.6" customWidth="1" min="10" max="10"/>
+    <col width="3.6" customWidth="1" min="11" max="11"/>
+    <col width="3.6" customWidth="1" min="12" max="12"/>
+    <col width="3.6" customWidth="1" min="13" max="13"/>
+    <col width="3.6" customWidth="1" min="14" max="14"/>
+    <col width="3.6" customWidth="1" min="15" max="15"/>
+    <col width="3.6" customWidth="1" min="16" max="16"/>
+    <col width="3.6" customWidth="1" min="17" max="17"/>
+    <col width="3.6" customWidth="1" min="18" max="18"/>
+    <col width="3.6" customWidth="1" min="19" max="19"/>
+    <col width="3.6" customWidth="1" min="20" max="20"/>
+    <col width="3.6" customWidth="1" min="21" max="21"/>
+    <col width="3.6" customWidth="1" min="22" max="22"/>
+    <col width="3.6" customWidth="1" min="23" max="23"/>
+    <col width="3.6" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="M1" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>도  서  표  지</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  도  서  명</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>수량산출서</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공  사  명</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  발 주 기 관</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>가나시 건설과</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  시  공  사</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>예시건설(주)</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  작 성 일 자</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="7" t="n">
+        <v>46294</v>
+      </c>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
+      <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="5" t="n"/>
+      <c r="S9" s="5" t="n"/>
+      <c r="T9" s="5" t="n"/>
+      <c r="U9" s="5" t="n"/>
+      <c r="V9" s="5" t="n"/>
+      <c r="W9" s="5" t="n"/>
+      <c r="X9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  작  성  자</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>예시건설(주) 공무팀</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+      <c r="Q10" s="5" t="n"/>
+      <c r="R10" s="5" t="n"/>
+      <c r="S10" s="5" t="n"/>
+      <c r="T10" s="5" t="n"/>
+      <c r="U10" s="5" t="n"/>
+      <c r="V10" s="5" t="n"/>
+      <c r="W10" s="5" t="n"/>
+      <c r="X10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  권 호 / 면 수</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>1권 (전 2권) / 248면</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
+      <c r="Q11" s="5" t="n"/>
+      <c r="R11" s="5" t="n"/>
+      <c r="S11" s="5" t="n"/>
+      <c r="T11" s="5" t="n"/>
+      <c r="U11" s="5" t="n"/>
+      <c r="V11" s="5" t="n"/>
+      <c r="W11" s="5" t="n"/>
+      <c r="X11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="6" customHeight="1"/>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>※ 아래는 목차입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>제        목</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
+      <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="5" t="n"/>
+      <c r="T15" s="5" t="n"/>
+      <c r="U15" s="5" t="n"/>
+      <c r="V15" s="9" t="inlineStr">
+        <is>
+          <t>면</t>
+        </is>
+      </c>
+      <c r="W15" s="5" t="n"/>
+      <c r="X15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="10">
+        <f>IF(C16="","",COUNTA(C16:C16))</f>
+        <v/>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>1. 총괄 집계표</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
+      <c r="Q16" s="5" t="n"/>
+      <c r="R16" s="5" t="n"/>
+      <c r="S16" s="5" t="n"/>
+      <c r="T16" s="5" t="n"/>
+      <c r="U16" s="5" t="n"/>
+      <c r="V16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" s="5" t="n"/>
+      <c r="X16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="10">
+        <f>IF(C17="","",COUNTA(C16:C17))</f>
+        <v/>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>2. 토공 수량산출</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
+      <c r="Q17" s="5" t="n"/>
+      <c r="R17" s="5" t="n"/>
+      <c r="S17" s="5" t="n"/>
+      <c r="T17" s="5" t="n"/>
+      <c r="U17" s="5" t="n"/>
+      <c r="V17" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="W17" s="5" t="n"/>
+      <c r="X17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="10">
+        <f>IF(C18="","",COUNTA(C16:C18))</f>
+        <v/>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>3. 배수공 수량산출</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
+      <c r="Q18" s="5" t="n"/>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" s="5" t="n"/>
+      <c r="T18" s="5" t="n"/>
+      <c r="U18" s="5" t="n"/>
+      <c r="V18" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="W18" s="5" t="n"/>
+      <c r="X18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="10">
+        <f>IF(C19="","",COUNTA(C16:C19))</f>
+        <v/>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>4. 구조물공 수량산출</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
+      <c r="Q19" s="5" t="n"/>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="5" t="n"/>
+      <c r="T19" s="5" t="n"/>
+      <c r="U19" s="5" t="n"/>
+      <c r="V19" s="12" t="n">
+        <v>118</v>
+      </c>
+      <c r="W19" s="5" t="n"/>
+      <c r="X19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="10">
+        <f>IF(C20="","",COUNTA(C16:C20))</f>
+        <v/>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>5. 포장공 수량산출</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="5" t="n"/>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="5" t="n"/>
+      <c r="T20" s="5" t="n"/>
+      <c r="U20" s="5" t="n"/>
+      <c r="V20" s="12" t="n">
+        <v>196</v>
+      </c>
+      <c r="W20" s="5" t="n"/>
+      <c r="X20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="10">
+        <f>IF(C21="","",COUNTA(C16:C21))</f>
+        <v/>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>6. 부대공 수량산출</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="5" t="n"/>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="5" t="n"/>
+      <c r="T21" s="5" t="n"/>
+      <c r="U21" s="5" t="n"/>
+      <c r="V21" s="12" t="n">
+        <v>231</v>
+      </c>
+      <c r="W21" s="5" t="n"/>
+      <c r="X21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="10">
+        <f>IF(C22="","",COUNTA(C16:C22))</f>
+        <v/>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
+      <c r="Q22" s="5" t="n"/>
+      <c r="R22" s="5" t="n"/>
+      <c r="S22" s="5" t="n"/>
+      <c r="T22" s="5" t="n"/>
+      <c r="U22" s="5" t="n"/>
+      <c r="V22" s="12" t="n"/>
+      <c r="W22" s="5" t="n"/>
+      <c r="X22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="10">
+        <f>IF(C23="","",COUNTA(C16:C23))</f>
+        <v/>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
+      <c r="Q23" s="5" t="n"/>
+      <c r="R23" s="5" t="n"/>
+      <c r="S23" s="5" t="n"/>
+      <c r="T23" s="5" t="n"/>
+      <c r="U23" s="5" t="n"/>
+      <c r="V23" s="12" t="n"/>
+      <c r="W23" s="5" t="n"/>
+      <c r="X23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="10">
+        <f>IF(C24="","",COUNTA(C16:C24))</f>
+        <v/>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
+      <c r="Q24" s="5" t="n"/>
+      <c r="R24" s="5" t="n"/>
+      <c r="S24" s="5" t="n"/>
+      <c r="T24" s="5" t="n"/>
+      <c r="U24" s="5" t="n"/>
+      <c r="V24" s="12" t="n"/>
+      <c r="W24" s="5" t="n"/>
+      <c r="X24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="10">
+        <f>IF(C25="","",COUNTA(C16:C25))</f>
+        <v/>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
+      <c r="Q25" s="5" t="n"/>
+      <c r="R25" s="5" t="n"/>
+      <c r="S25" s="5" t="n"/>
+      <c r="T25" s="5" t="n"/>
+      <c r="U25" s="5" t="n"/>
+      <c r="V25" s="12" t="n"/>
+      <c r="W25" s="5" t="n"/>
+      <c r="X25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="10">
+        <f>IF(C26="","",COUNTA(C16:C26))</f>
+        <v/>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
+      <c r="Q26" s="5" t="n"/>
+      <c r="R26" s="5" t="n"/>
+      <c r="S26" s="5" t="n"/>
+      <c r="T26" s="5" t="n"/>
+      <c r="U26" s="5" t="n"/>
+      <c r="V26" s="12" t="n"/>
+      <c r="W26" s="5" t="n"/>
+      <c r="X26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="10">
+        <f>IF(C27="","",COUNTA(C16:C27))</f>
+        <v/>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
+      <c r="Q27" s="5" t="n"/>
+      <c r="R27" s="5" t="n"/>
+      <c r="S27" s="5" t="n"/>
+      <c r="T27" s="5" t="n"/>
+      <c r="U27" s="5" t="n"/>
+      <c r="V27" s="12" t="n"/>
+      <c r="W27" s="5" t="n"/>
+      <c r="X27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="10">
+        <f>IF(C28="","",COUNTA(C16:C28))</f>
+        <v/>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
+      <c r="Q28" s="5" t="n"/>
+      <c r="R28" s="5" t="n"/>
+      <c r="S28" s="5" t="n"/>
+      <c r="T28" s="5" t="n"/>
+      <c r="U28" s="5" t="n"/>
+      <c r="V28" s="12" t="n"/>
+      <c r="W28" s="5" t="n"/>
+      <c r="X28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="10">
+        <f>IF(C29="","",COUNTA(C16:C29))</f>
+        <v/>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="5" t="n"/>
+      <c r="Q29" s="5" t="n"/>
+      <c r="R29" s="5" t="n"/>
+      <c r="S29" s="5" t="n"/>
+      <c r="T29" s="5" t="n"/>
+      <c r="U29" s="5" t="n"/>
+      <c r="V29" s="12" t="n"/>
+      <c r="W29" s="5" t="n"/>
+      <c r="X29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="10" customHeight="1"/>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="13" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="14" t="inlineStr"/>
+      <c r="K33" s="15" t="inlineStr">
+        <is>
+          <t>현장대리인</t>
+        </is>
+      </c>
+      <c r="Q33" s="16" t="inlineStr">
+        <is>
+          <t>김철수</t>
+        </is>
+      </c>
+      <c r="U33" s="17" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="69">
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="V28:X28"/>
+    <mergeCell ref="V24:X24"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="G7:X7"/>
+    <mergeCell ref="C27:U27"/>
+    <mergeCell ref="U33:X33"/>
+    <mergeCell ref="C23:U23"/>
+    <mergeCell ref="G10:X10"/>
+    <mergeCell ref="C17:U17"/>
+    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="G6:X6"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C19:U19"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="V27:X27"/>
+    <mergeCell ref="C28:U28"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:X5"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="C18:U18"/>
+    <mergeCell ref="V26:X26"/>
+    <mergeCell ref="C21:U21"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A32:X32"/>
+    <mergeCell ref="V25:X25"/>
+    <mergeCell ref="C24:U24"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="C15:U15"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="Q33:T33"/>
+    <mergeCell ref="V22:X22"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="C26:U26"/>
+    <mergeCell ref="V18:X18"/>
+    <mergeCell ref="C29:U29"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="G9:X9"/>
+    <mergeCell ref="A13:X13"/>
+    <mergeCell ref="V17:X17"/>
+    <mergeCell ref="C20:U20"/>
+    <mergeCell ref="V21:X21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:U16"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C25:U25"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="G11:X11"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C22:U22"/>
+    <mergeCell ref="V23:X23"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="M1:X1"/>
+    <mergeCell ref="V20:X20"/>
+    <mergeCell ref="A36:X36"/>
+    <mergeCell ref="V29:X29"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G8:X8"/>
+    <mergeCell ref="V19:X19"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/doseo-pyoji.xlsx
+++ b/web/public/forms/doseo-pyoji.xlsx
@@ -586,7 +586,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1427,7 +1427,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="19" t="inlineStr">
@@ -2277,6 +2277,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/doseo-pyoji.xlsx
+++ b/web/public/forms/doseo-pyoji.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="도서 표지 모음" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'도서 표지 모음'!$A$1:$X$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -132,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -185,9 +183,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -866,10 +861,7 @@
       <c r="X15" s="5" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="10">
-        <f>IF(C16="","",COUNTA(C16:C16))</f>
-        <v/>
-      </c>
+      <c r="A16" s="10" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="11" t="n"/>
       <c r="D16" s="5" t="n"/>
@@ -895,10 +887,7 @@
       <c r="X16" s="5" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="10">
-        <f>IF(C17="","",COUNTA(C16:C17))</f>
-        <v/>
-      </c>
+      <c r="A17" s="10" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="11" t="n"/>
       <c r="D17" s="5" t="n"/>
@@ -924,10 +913,7 @@
       <c r="X17" s="5" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="10">
-        <f>IF(C18="","",COUNTA(C16:C18))</f>
-        <v/>
-      </c>
+      <c r="A18" s="10" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="11" t="n"/>
       <c r="D18" s="5" t="n"/>
@@ -953,10 +939,7 @@
       <c r="X18" s="5" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="10">
-        <f>IF(C19="","",COUNTA(C16:C19))</f>
-        <v/>
-      </c>
+      <c r="A19" s="10" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="11" t="n"/>
       <c r="D19" s="5" t="n"/>
@@ -982,10 +965,7 @@
       <c r="X19" s="5" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="10">
-        <f>IF(C20="","",COUNTA(C16:C20))</f>
-        <v/>
-      </c>
+      <c r="A20" s="10" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="11" t="n"/>
       <c r="D20" s="5" t="n"/>
@@ -1011,10 +991,7 @@
       <c r="X20" s="5" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="10">
-        <f>IF(C21="","",COUNTA(C16:C21))</f>
-        <v/>
-      </c>
+      <c r="A21" s="10" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="11" t="n"/>
       <c r="D21" s="5" t="n"/>
@@ -1040,10 +1017,7 @@
       <c r="X21" s="5" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="10">
-        <f>IF(C22="","",COUNTA(C16:C22))</f>
-        <v/>
-      </c>
+      <c r="A22" s="10" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="11" t="n"/>
       <c r="D22" s="5" t="n"/>
@@ -1069,10 +1043,7 @@
       <c r="X22" s="5" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="10">
-        <f>IF(C23="","",COUNTA(C16:C23))</f>
-        <v/>
-      </c>
+      <c r="A23" s="10" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="11" t="n"/>
       <c r="D23" s="5" t="n"/>
@@ -1098,10 +1069,7 @@
       <c r="X23" s="5" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="10">
-        <f>IF(C24="","",COUNTA(C16:C24))</f>
-        <v/>
-      </c>
+      <c r="A24" s="10" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="5" t="n"/>
@@ -1127,10 +1095,7 @@
       <c r="X24" s="5" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="10">
-        <f>IF(C25="","",COUNTA(C16:C25))</f>
-        <v/>
-      </c>
+      <c r="A25" s="10" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="5" t="n"/>
@@ -1156,10 +1121,7 @@
       <c r="X25" s="5" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="10">
-        <f>IF(C26="","",COUNTA(C16:C26))</f>
-        <v/>
-      </c>
+      <c r="A26" s="10" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="5" t="n"/>
@@ -1185,10 +1147,7 @@
       <c r="X26" s="5" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="10">
-        <f>IF(C27="","",COUNTA(C16:C27))</f>
-        <v/>
-      </c>
+      <c r="A27" s="10" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="5" t="n"/>
@@ -1214,10 +1173,7 @@
       <c r="X27" s="5" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="10">
-        <f>IF(C28="","",COUNTA(C16:C28))</f>
-        <v/>
-      </c>
+      <c r="A28" s="10" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="11" t="n"/>
       <c r="D28" s="5" t="n"/>
@@ -1243,10 +1199,7 @@
       <c r="X28" s="5" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="10">
-        <f>IF(C29="","",COUNTA(C16:C29))</f>
-        <v/>
-      </c>
+      <c r="A29" s="10" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="11" t="n"/>
       <c r="D29" s="5" t="n"/>
@@ -1295,6 +1248,7 @@
       </c>
     </row>
     <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="18" t="inlineStr">
         <is>
@@ -1386,897 +1340,4 @@
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>도  서  표  지</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  도  서  명</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>수량산출서</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공  사  명</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  발 주 기 관</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>가나시 건설과</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  시  공  사</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>예시건설(주)</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  작 성 일 자</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="7" t="n">
-        <v>46294</v>
-      </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
-      <c r="T9" s="5" t="n"/>
-      <c r="U9" s="5" t="n"/>
-      <c r="V9" s="5" t="n"/>
-      <c r="W9" s="5" t="n"/>
-      <c r="X9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  작  성  자</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>예시건설(주) 공무팀</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="5" t="n"/>
-      <c r="Q10" s="5" t="n"/>
-      <c r="R10" s="5" t="n"/>
-      <c r="S10" s="5" t="n"/>
-      <c r="T10" s="5" t="n"/>
-      <c r="U10" s="5" t="n"/>
-      <c r="V10" s="5" t="n"/>
-      <c r="W10" s="5" t="n"/>
-      <c r="X10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  권 호 / 면 수</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>1권 (전 2권) / 248면</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-      <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="5" t="n"/>
-      <c r="R11" s="5" t="n"/>
-      <c r="S11" s="5" t="n"/>
-      <c r="T11" s="5" t="n"/>
-      <c r="U11" s="5" t="n"/>
-      <c r="V11" s="5" t="n"/>
-      <c r="W11" s="5" t="n"/>
-      <c r="X11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="6" customHeight="1"/>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>※ 아래는 목차입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="6" customHeight="1"/>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>제        목</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="5" t="n"/>
-      <c r="S15" s="5" t="n"/>
-      <c r="T15" s="5" t="n"/>
-      <c r="U15" s="5" t="n"/>
-      <c r="V15" s="9" t="inlineStr">
-        <is>
-          <t>면</t>
-        </is>
-      </c>
-      <c r="W15" s="5" t="n"/>
-      <c r="X15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="10">
-        <f>IF(C16="","",COUNTA(C16:C16))</f>
-        <v/>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>1. 총괄 집계표</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-      <c r="P16" s="5" t="n"/>
-      <c r="Q16" s="5" t="n"/>
-      <c r="R16" s="5" t="n"/>
-      <c r="S16" s="5" t="n"/>
-      <c r="T16" s="5" t="n"/>
-      <c r="U16" s="5" t="n"/>
-      <c r="V16" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="W16" s="5" t="n"/>
-      <c r="X16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="10">
-        <f>IF(C17="","",COUNTA(C16:C17))</f>
-        <v/>
-      </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>2. 토공 수량산출</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-      <c r="P17" s="5" t="n"/>
-      <c r="Q17" s="5" t="n"/>
-      <c r="R17" s="5" t="n"/>
-      <c r="S17" s="5" t="n"/>
-      <c r="T17" s="5" t="n"/>
-      <c r="U17" s="5" t="n"/>
-      <c r="V17" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="W17" s="5" t="n"/>
-      <c r="X17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="10">
-        <f>IF(C18="","",COUNTA(C16:C18))</f>
-        <v/>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>3. 배수공 수량산출</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" s="5" t="n"/>
-      <c r="T18" s="5" t="n"/>
-      <c r="U18" s="5" t="n"/>
-      <c r="V18" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="W18" s="5" t="n"/>
-      <c r="X18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="10">
-        <f>IF(C19="","",COUNTA(C16:C19))</f>
-        <v/>
-      </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>4. 구조물공 수량산출</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="5" t="n"/>
-      <c r="R19" s="5" t="n"/>
-      <c r="S19" s="5" t="n"/>
-      <c r="T19" s="5" t="n"/>
-      <c r="U19" s="5" t="n"/>
-      <c r="V19" s="12" t="n">
-        <v>118</v>
-      </c>
-      <c r="W19" s="5" t="n"/>
-      <c r="X19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="10">
-        <f>IF(C20="","",COUNTA(C16:C20))</f>
-        <v/>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>5. 포장공 수량산출</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="5" t="n"/>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" s="5" t="n"/>
-      <c r="T20" s="5" t="n"/>
-      <c r="U20" s="5" t="n"/>
-      <c r="V20" s="12" t="n">
-        <v>196</v>
-      </c>
-      <c r="W20" s="5" t="n"/>
-      <c r="X20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="10">
-        <f>IF(C21="","",COUNTA(C16:C21))</f>
-        <v/>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>6. 부대공 수량산출</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="5" t="n"/>
-      <c r="T21" s="5" t="n"/>
-      <c r="U21" s="5" t="n"/>
-      <c r="V21" s="12" t="n">
-        <v>231</v>
-      </c>
-      <c r="W21" s="5" t="n"/>
-      <c r="X21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="10">
-        <f>IF(C22="","",COUNTA(C16:C22))</f>
-        <v/>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="5" t="n"/>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="5" t="n"/>
-      <c r="T22" s="5" t="n"/>
-      <c r="U22" s="5" t="n"/>
-      <c r="V22" s="12" t="n"/>
-      <c r="W22" s="5" t="n"/>
-      <c r="X22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="10">
-        <f>IF(C23="","",COUNTA(C16:C23))</f>
-        <v/>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-      <c r="P23" s="5" t="n"/>
-      <c r="Q23" s="5" t="n"/>
-      <c r="R23" s="5" t="n"/>
-      <c r="S23" s="5" t="n"/>
-      <c r="T23" s="5" t="n"/>
-      <c r="U23" s="5" t="n"/>
-      <c r="V23" s="12" t="n"/>
-      <c r="W23" s="5" t="n"/>
-      <c r="X23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="10">
-        <f>IF(C24="","",COUNTA(C16:C24))</f>
-        <v/>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-      <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="5" t="n"/>
-      <c r="R24" s="5" t="n"/>
-      <c r="S24" s="5" t="n"/>
-      <c r="T24" s="5" t="n"/>
-      <c r="U24" s="5" t="n"/>
-      <c r="V24" s="12" t="n"/>
-      <c r="W24" s="5" t="n"/>
-      <c r="X24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="10">
-        <f>IF(C25="","",COUNTA(C16:C25))</f>
-        <v/>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-      <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="5" t="n"/>
-      <c r="R25" s="5" t="n"/>
-      <c r="S25" s="5" t="n"/>
-      <c r="T25" s="5" t="n"/>
-      <c r="U25" s="5" t="n"/>
-      <c r="V25" s="12" t="n"/>
-      <c r="W25" s="5" t="n"/>
-      <c r="X25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="10">
-        <f>IF(C26="","",COUNTA(C16:C26))</f>
-        <v/>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-      <c r="P26" s="5" t="n"/>
-      <c r="Q26" s="5" t="n"/>
-      <c r="R26" s="5" t="n"/>
-      <c r="S26" s="5" t="n"/>
-      <c r="T26" s="5" t="n"/>
-      <c r="U26" s="5" t="n"/>
-      <c r="V26" s="12" t="n"/>
-      <c r="W26" s="5" t="n"/>
-      <c r="X26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="10">
-        <f>IF(C27="","",COUNTA(C16:C27))</f>
-        <v/>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-      <c r="P27" s="5" t="n"/>
-      <c r="Q27" s="5" t="n"/>
-      <c r="R27" s="5" t="n"/>
-      <c r="S27" s="5" t="n"/>
-      <c r="T27" s="5" t="n"/>
-      <c r="U27" s="5" t="n"/>
-      <c r="V27" s="12" t="n"/>
-      <c r="W27" s="5" t="n"/>
-      <c r="X27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="10">
-        <f>IF(C28="","",COUNTA(C16:C28))</f>
-        <v/>
-      </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="n"/>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="n"/>
-      <c r="P28" s="5" t="n"/>
-      <c r="Q28" s="5" t="n"/>
-      <c r="R28" s="5" t="n"/>
-      <c r="S28" s="5" t="n"/>
-      <c r="T28" s="5" t="n"/>
-      <c r="U28" s="5" t="n"/>
-      <c r="V28" s="12" t="n"/>
-      <c r="W28" s="5" t="n"/>
-      <c r="X28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="10">
-        <f>IF(C29="","",COUNTA(C16:C29))</f>
-        <v/>
-      </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-      <c r="O29" s="5" t="n"/>
-      <c r="P29" s="5" t="n"/>
-      <c r="Q29" s="5" t="n"/>
-      <c r="R29" s="5" t="n"/>
-      <c r="S29" s="5" t="n"/>
-      <c r="T29" s="5" t="n"/>
-      <c r="U29" s="5" t="n"/>
-      <c r="V29" s="12" t="n"/>
-      <c r="W29" s="5" t="n"/>
-      <c r="X29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="6" customHeight="1"/>
-    <row r="31" ht="10" customHeight="1"/>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="13" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="14" t="inlineStr"/>
-      <c r="K33" s="15" t="inlineStr">
-        <is>
-          <t>현장대리인</t>
-        </is>
-      </c>
-      <c r="Q33" s="16" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="U33" s="17" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="6" customHeight="1"/>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="18" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="69">
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="V28:X28"/>
-    <mergeCell ref="V24:X24"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="G7:X7"/>
-    <mergeCell ref="C27:U27"/>
-    <mergeCell ref="U33:X33"/>
-    <mergeCell ref="C23:U23"/>
-    <mergeCell ref="G10:X10"/>
-    <mergeCell ref="C17:U17"/>
-    <mergeCell ref="A33:J33"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C19:U19"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="V27:X27"/>
-    <mergeCell ref="C28:U28"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="C18:U18"/>
-    <mergeCell ref="V26:X26"/>
-    <mergeCell ref="C21:U21"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A32:X32"/>
-    <mergeCell ref="V25:X25"/>
-    <mergeCell ref="C24:U24"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="C15:U15"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="Q33:T33"/>
-    <mergeCell ref="V22:X22"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="C26:U26"/>
-    <mergeCell ref="V18:X18"/>
-    <mergeCell ref="C29:U29"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="G9:X9"/>
-    <mergeCell ref="A13:X13"/>
-    <mergeCell ref="V17:X17"/>
-    <mergeCell ref="C20:U20"/>
-    <mergeCell ref="V21:X21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:U16"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C25:U25"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="G11:X11"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C22:U22"/>
-    <mergeCell ref="V23:X23"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="V20:X20"/>
-    <mergeCell ref="A36:X36"/>
-    <mergeCell ref="V29:X29"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G8:X8"/>
-    <mergeCell ref="V19:X19"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/doseo-pyoji.xlsx
+++ b/web/public/forms/doseo-pyoji.xlsx
@@ -581,7 +581,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
